--- a/artfynd/A 5220-2023 artfynd.xlsx
+++ b/artfynd/A 5220-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123428641</v>
       </c>
       <c r="B2" t="n">
-        <v>106911</v>
+        <v>106917</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 5220-2023 artfynd.xlsx
+++ b/artfynd/A 5220-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123428641</v>
       </c>
       <c r="B2" t="n">
-        <v>106920</v>
+        <v>106937</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 5220-2023 artfynd.xlsx
+++ b/artfynd/A 5220-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123428641</v>
       </c>
       <c r="B2" t="n">
-        <v>106937</v>
+        <v>106955</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 5220-2023 artfynd.xlsx
+++ b/artfynd/A 5220-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123428641</v>
       </c>
       <c r="B2" t="n">
-        <v>106955</v>
+        <v>106957</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 5220-2023 artfynd.xlsx
+++ b/artfynd/A 5220-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123428641</v>
       </c>
       <c r="B2" t="n">
-        <v>106957</v>
+        <v>106532</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 5220-2023 artfynd.xlsx
+++ b/artfynd/A 5220-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123428641</v>
       </c>
       <c r="B2" t="n">
-        <v>106532</v>
+        <v>106533</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
